--- a/LubanData/Data/__enums__.xlsx
+++ b/LubanData/Data/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc34d4f127b14b47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra246e79262a14f83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -471,16 +471,16 @@
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="str">
-        <x:v>Normal</x:v>
+        <x:v>Chick</x:v>
       </x:c>
       <x:c r="I4" s="5" t="str">
-        <x:v>普通</x:v>
+        <x:v>小鸡</x:v>
       </x:c>
       <x:c r="J4" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="5" t="str">
-        <x:v>普通敌人</x:v>
+        <x:v>小鸡敌人</x:v>
       </x:c>
       <x:c r="L4" s="5"/>
     </x:row>
@@ -493,16 +493,16 @@
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="str">
-        <x:v>Elite</x:v>
+        <x:v>Hen</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>精英</x:v>
+        <x:v>母鸡</x:v>
       </x:c>
       <x:c r="J5" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K5" s="5" t="str">
-        <x:v>精英敌人</x:v>
+        <x:v>母鸡敌人</x:v>
       </x:c>
       <x:c r="L5" s="5"/>
     </x:row>
@@ -515,16 +515,16 @@
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5" t="str">
-        <x:v>Boss</x:v>
+        <x:v>Rooster</x:v>
       </x:c>
       <x:c r="I6" s="5" t="str">
-        <x:v>首领</x:v>
+        <x:v>公鸡</x:v>
       </x:c>
       <x:c r="J6" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K6" s="5" t="str">
-        <x:v>首领敌人</x:v>
+        <x:v>公鸡敌人</x:v>
       </x:c>
       <x:c r="L6" s="5"/>
     </x:row>

--- a/LubanData/Data/__enums__.xlsx
+++ b/LubanData/Data/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra246e79262a14f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc8fa60e10df34e7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -528,6 +528,28 @@
       </x:c>
       <x:c r="L6" s="5"/>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7" t="str">
+        <x:v>Ikun</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>坤</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>ikun 敌人</x:v>
+      </x:c>
+      <x:c r="L7"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>

--- a/LubanData/Data/__enums__.xlsx
+++ b/LubanData/Data/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc8fa60e10df34e7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R933e10911f8641e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -550,6 +550,80 @@
       </x:c>
       <x:c r="L7"/>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8" t="str">
+        <x:v>game.PropType</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8" t="str">
+        <x:v>道具类型</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8" t="str">
+        <x:v>WeaponBox</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>武器箱</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>武器箱道具</x:v>
+      </x:c>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9" t="str">
+        <x:v>Basketball</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>篮球</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>篮球道具</x:v>
+      </x:c>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10" t="str">
+        <x:v>GooseCage</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>鹅笼</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>鹅笼道具</x:v>
+      </x:c>
+      <x:c r="L10"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>
